--- a/data/trans_dic/P64D$otros_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,12 +572,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,62</t>
+          <t>0,38; 3,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,02</t>
+          <t>0,44; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,8</t>
+          <t>0,64; 2,84</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,84</t>
+          <t>0,32; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,6</t>
+          <t>0,27; 1,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,08</t>
+          <t>0,03; 1,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,33</t>
+          <t>0,15; 1,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,0</t>
+          <t>0,14; 0,96</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,92</t>
+          <t>0,37; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,65</t>
+          <t>0,2; 1,64</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,45</t>
+          <t>0,0; 22,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 10,51</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,4</t>
+          <t>0,42; 1,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,16</t>
+          <t>0,31; 1,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,1</t>
+          <t>0,49; 1,11</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3610</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 715</t>
+          <t>0; 1265</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 884</t>
+          <t>0; 881</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1203; 12670</t>
+          <t>1341; 13844</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1331; 14070</t>
+          <t>1534; 13823</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3969; 19633</t>
+          <t>4457; 19909</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1489; 13140</t>
+          <t>1487; 12886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3769</t>
+          <t>0; 4508</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2372; 13040</t>
+          <t>2220; 14271</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>247; 8015</t>
+          <t>238; 8414</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>659; 6033</t>
+          <t>672; 7038</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1733; 11946</t>
+          <t>1628; 11441</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1069; 8729</t>
+          <t>1099; 8336</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1027</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>921; 8391</t>
+          <t>1031; 8328</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 3855</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 892</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3584</t>
+          <t>0; 3645</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8230; 27537</t>
+          <t>8286; 27774</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4348; 16983</t>
+          <t>4559; 16711</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15689; 37855</t>
+          <t>16684; 38207</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$otros_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 12,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,95</t>
+          <t>0,46; 3,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,95</t>
+          <t>0,63; 4,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,84</t>
+          <t>0,76; 3,15</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,79</t>
+          <t>0,4; 2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,75</t>
+          <t>0,35; 1,65</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,13</t>
+          <t>0,17; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,55</t>
+          <t>0,15; 1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,96</t>
+          <t>0,3; 1,48</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,79</t>
+          <t>0,49; 2,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,64</t>
+          <t>0,28; 1,73</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,75</t>
+          <t>0,0; 19,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,51</t>
+          <t>0,0; 10,34</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,41</t>
+          <t>0,7; 1,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,14</t>
+          <t>0,47; 1,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,11</t>
+          <t>0,67; 1,42</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2263</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1265</t>
+          <t>0; 11260</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 881</t>
+          <t>0; 13857</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>12188</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1341; 13844</t>
+          <t>1814; 13040</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1534; 13823</t>
+          <t>1974; 14491</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4457; 19909</t>
+          <t>5437; 22398</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>7679</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1487; 12886</t>
+          <t>2134; 12741</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4508</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2220; 14271</t>
+          <t>3288; 15368</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>7205</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238; 8414</t>
+          <t>927; 11264</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>672; 7038</t>
+          <t>697; 6640</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1628; 11441</t>
+          <t>3012; 14784</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4327</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1099; 8336</t>
+          <t>1599; 9000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1031; 8328</t>
+          <t>1590; 9672</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3855</t>
+          <t>0; 3773</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>0; 4022</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8286; 27774</t>
+          <t>13532; 33169</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4559; 16711</t>
+          <t>7113; 24994</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16684; 38207</t>
+          <t>23200; 48742</t>
         </is>
       </c>
     </row>
